--- a/simplifiedDebts.xlsx
+++ b/simplifiedDebts.xlsx
@@ -413,258 +413,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AJ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Person 1</t>
+          <t>Person 2</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Person 2</t>
+          <t>Person 3</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Person 3</t>
+          <t>Person 5</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Person 4</t>
+          <t>Person 6</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Person 5</t>
+          <t>Person 7</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Person 6</t>
+          <t>Person 8</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Person 7</t>
+          <t>Person 10</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Person 8</t>
+          <t>Person 11</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Person 9</t>
+          <t>Person 13</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Person 10</t>
+          <t>Person 14</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Person 11</t>
+          <t>Person 15</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Person 12</t>
+          <t>Person 16</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Person 13</t>
+          <t>Person 17</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Person 14</t>
+          <t>Person 19</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Person 15</t>
+          <t>Person 20</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Person 16</t>
+          <t>Person 21</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Person 17</t>
+          <t>Person 22</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Person 18</t>
+          <t>Person 23</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Person 19</t>
+          <t>Person 24</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Person 20</t>
+          <t>Person 25</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Person 21</t>
+          <t>Person 27</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Person 22</t>
+          <t>Person 28</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Person 23</t>
+          <t>Person 32</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Person 24</t>
+          <t>Person 33</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Person 25</t>
+          <t>Person 34</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Person 26</t>
+          <t>Person 36</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Person 27</t>
+          <t>Person 37</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Person 28</t>
+          <t>Person 38</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Person 29</t>
+          <t>Person 39</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Person 30</t>
+          <t>Person 41</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Person 31</t>
+          <t>Person 42</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Person 32</t>
+          <t>Person 43</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Person 33</t>
+          <t>Person 45</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Person 34</t>
+          <t>Person 47</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Person 35</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Person 36</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Person 37</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Person 38</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Person 39</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Person 40</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Person 41</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Person 42</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Person 43</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Person 44</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Person 45</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Person 46</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Person 47</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
           <t>Person 48</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Person 49</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Person 50</t>
         </is>
       </c>
     </row>
@@ -678,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>109.16</v>
       </c>
       <c r="D2" t="n">
-        <v>109.16</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -765,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>60.63</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -777,52 +702,7 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
         <v>57.55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -835,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>291.28</v>
       </c>
       <c r="D3" t="n">
-        <v>291.28</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -865,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>45.39</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -877,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>45.39</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -934,51 +814,6 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,10 +824,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>425.87</v>
       </c>
       <c r="C4" t="n">
-        <v>425.87</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1007,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>132.69</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1016,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.69</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1091,52 +926,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
         <v>18.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1212,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>114.43</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1239,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>114.43</v>
+        <v>158.44</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1248,51 +1038,6 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>158.44</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1312,13 +1057,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>88.14</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>88.14</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1399,57 +1144,12 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>8.34</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>75.06</v>
       </c>
       <c r="D7" t="n">
-        <v>75.06</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1478,16 +1178,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>155.09</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>50.95</v>
       </c>
       <c r="K7" t="n">
-        <v>155.09</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1496,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>50.95</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1508,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1523,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>91.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1544,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>155.35</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1562,51 +1262,6 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>155.35</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1623,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>62.49</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>62.49</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1719,51 +1374,6 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1807,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>154.08</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1819,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>154.08</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>37.23</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1837,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>37.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1876,51 +1486,6 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1937,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>123.58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>123.58</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1973,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>163.18</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1988,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>163.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2009,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>314.08</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2021,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2033,51 +1598,6 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>314.08</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2121,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>316.03</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2133,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>316.03</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2166,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2190,51 +1710,6 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>89.45999999999999</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2245,10 +1720,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2257,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>45.99</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>45.99</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2281,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>110.83</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2293,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>110.83</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2302,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>134.76</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2317,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>134.76</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2347,51 +1822,6 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2405,19 +1835,19 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="D13" t="n">
-        <v>1.529999999999993</v>
+        <v>92.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>163.77</v>
       </c>
       <c r="F13" t="n">
-        <v>92.8</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>163.77</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2432,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>106.52</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2444,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>106.52</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2486,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>130.06</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2504,51 +1934,6 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>130.06</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2562,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>73.16</v>
       </c>
       <c r="D14" t="n">
-        <v>73.16</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2574,13 +1959,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>178.04</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>178.04</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2589,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>93.43000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2613,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>122.1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2628,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>122.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2661,51 +2046,6 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2725,19 +2065,19 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>132.83</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>132.83</v>
+        <v>39.44</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>39.44</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2818,51 +2158,6 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2873,25 +2168,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1599999999999965</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>21.17</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>48.68</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2900,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48.68</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2909,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>40.95</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2921,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>40.95</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2939,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2966,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>18.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2975,51 +2270,6 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3042,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>163.73</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>163.73</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3057,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>96.31</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>66.83</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3069,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>96.31</v>
+        <v>114.07</v>
       </c>
       <c r="P17" t="n">
-        <v>66.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3084,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>114.07</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -3096,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -3120,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>142.19</v>
       </c>
       <c r="AG17" t="n">
-        <v>91.51000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -3132,51 +2382,6 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>142.19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3190,22 +2395,22 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>89.05</v>
       </c>
       <c r="D18" t="n">
-        <v>89.05</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>68.45</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>68.45</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3289,51 +2494,6 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3359,13 +2519,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>154.45</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>154.45</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3389,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>119.13</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -3404,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>119.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3422,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>44.22</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3446,51 +2606,6 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>44.22</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3504,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>85.95</v>
       </c>
       <c r="D20" t="n">
-        <v>85.95</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -3537,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3549,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -3579,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>46.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3603,51 +2718,6 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3676,25 +2746,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>94.75</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7.129999999999993</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>94.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>47.67</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3706,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>47.67</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3760,51 +2830,6 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3815,10 +2840,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>80.01000000000001</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -3866,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>62.14</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -3881,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>62.14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3899,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>108.18</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3917,51 +2942,6 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>108.18</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3993,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>16.38</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -4002,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>16.38</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4014,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>73.41</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4023,13 +3003,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>37.43</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>73.41</v>
+        <v>103.41</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4038,13 +3018,13 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>37.43</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>103.41</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -4074,52 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
         <v>207.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4138,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -4153,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>160.83</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>94.52</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -4165,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>160.83</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>94.52</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -4183,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>25.95</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -4198,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>25.95</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -4231,51 +3166,6 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4316,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4328,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4388,51 +3278,6 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4443,13 +3288,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1699999999999965</v>
+        <v>9.84</v>
       </c>
       <c r="D26" t="n">
-        <v>9.84</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -4545,51 +3390,6 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4633,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>206.12</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4645,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>206.12</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -4657,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>64.94</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4672,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>64.94</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>38.83</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4699,54 +3499,9 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>164.35</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>164.35</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4802,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>40.54</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4817,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>40.54</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -4859,58 +3614,13 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
         <v>12.9</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Person 28</t>
+          <t>Person 29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4962,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4989,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>152.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>129.82</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5016,58 +3726,13 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Person 29</t>
+          <t>Person 30</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5080,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>28.14</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -5095,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>147.62</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -5104,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>34.26</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -5134,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -5173,58 +3838,13 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>152.2</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>129.82</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Person 30</t>
+          <t>Person 31</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5243,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>28.14</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -5264,16 +3884,16 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>147.62</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>38.78</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34.26</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -5306,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>169.29</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5327,61 +3947,16 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>48.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Person 31</t>
+          <t>Person 32</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -5430,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>186.13</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -5439,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>38.78</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -5466,79 +4041,34 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>13.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>150.02</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>31.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>21.38</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>169.29</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>48.95</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Person 32</t>
+          <t>Person 33</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5572,13 +4102,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>22.02</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>32.87</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5602,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>186.13</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5644,58 +4174,13 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>150.02</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Person 33</t>
+          <t>Person 35</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -5741,13 +4226,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>22.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>32.87</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5768,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5786,73 +4271,28 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>151.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>114.45</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>15.81</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
+        <v>129.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Person 34</t>
+          <t>Person 37</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5868,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5931,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>26.87</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5958,58 +4398,13 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Person 35</t>
+          <t>Person 38</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6019,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -6046,13 +4441,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>32.31</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -6073,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>47.67</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6109,64 +4504,19 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>151.33</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>114.45</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>129.51</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Person 36</t>
+          <t>Person 39</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6194,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>31.04</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -6206,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>49.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -6215,13 +4565,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>8.59</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>33.34</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -6272,58 +4622,13 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Person 37</t>
+          <t>Person 40</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6345,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>19.2</v>
+        <v>21.65</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -6378,16 +4683,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>30.23</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>104.5</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>111.62</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -6423,64 +4728,19 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>18.49</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>26.87</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>28.97</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Person 38</t>
+          <t>Person 41</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6496,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>98.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -6529,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>32.31</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -6538,13 +4798,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>24.48</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -6562,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>47.67</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6586,58 +4846,13 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Person 39</t>
+          <t>Person 42</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6659,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -6671,13 +4886,13 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>55.22</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>31.04</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6689,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>49.74</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -6701,13 +4916,13 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>8.59</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>33.34</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -6743,58 +4958,13 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Person 40</t>
+          <t>Person 43</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6816,22 +4986,22 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>58.22</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>13.21</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>21.65</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6864,19 +5034,19 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>30.23</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>104.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>55.53</v>
       </c>
       <c r="AB41" t="n">
-        <v>111.62</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -6900,58 +5070,13 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>18.49</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Person 41</t>
+          <t>Person 44</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6985,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>44.19</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -7018,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>100.93</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -7033,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7054,61 +5179,16 @@
         <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>55.23</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Person 42</t>
+          <t>Person 45</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7139,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -7151,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="P43" t="n">
-        <v>55.22</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7214,58 +5294,13 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Person 43</t>
+          <t>Person 46</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7284,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>18.37</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -7296,10 +5331,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>58.22</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>13.21</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -7308,13 +5343,13 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>113.97</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.620000000000007</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -7350,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>40.09</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -7371,58 +5406,13 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>55.53</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Person 44</t>
+          <t>Person 47</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7441,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>98.28</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -7468,13 +5458,13 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>44.19</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -7507,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>100.93</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -7528,58 +5518,13 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>94.16</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Person 45</t>
+          <t>Person 49</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7637,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>65.63</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -7682,61 +5627,16 @@
         <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Person 46</t>
+          <t>Person 50</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7761,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>18.37</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -7794,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>113.97</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -7812,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>19.13</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7833,688 +5733,15 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>73.22</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Person 47</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>98.28</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>9</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Person 48</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Person 49</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.61999999999999</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Person 50</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>19.13</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
         <v>0</v>
       </c>
     </row>
